--- a/out/Attention-mamba2_repeat_3_000002.xlsx
+++ b/out/Attention-mamba2_repeat_3_000002.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.443095189965484</v>
+        <v>8.62785843586423</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.443095189965484</v>
+        <v>8.62785843586423</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.443095189965484</v>
+        <v>9.227858435864231</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.443095189965484</v>
+        <v>0.0804624974787484</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.443095189965484</v>
+        <v>0.0804624974787484</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,14 +35917,14 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,14 +36712,14 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37511,10 +37511,10 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38306,10 +38306,10 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39101,10 +39101,10 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39896,10 +39896,10 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40691,10 +40691,10 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41486,10 +41486,10 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42281,10 +42281,10 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43079,7 +43079,7 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43871,10 +43871,10 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44666,10 +44666,10 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45461,10 +45461,10 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46256,10 +46256,10 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47051,10 +47051,10 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47846,10 +47846,10 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48641,10 +48641,10 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49436,10 +49436,10 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50231,10 +50231,10 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51026,10 +51026,10 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51821,10 +51821,10 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52616,10 +52616,10 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53414,7 +53414,7 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54209,7 +54209,7 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55004,7 +55004,7 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55796,10 +55796,10 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56591,10 +56591,10 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57386,10 +57386,10 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58181,10 +58181,10 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58976,10 +58976,10 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59771,10 +59771,10 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60566,10 +60566,10 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61364,7 +61364,7 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62159,7 +62159,7 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62951,10 +62951,10 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63749,7 +63749,7 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64544,7 +64544,7 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65332,14 +65332,14 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA81" t="n">
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66127,14 +66127,14 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA82" t="n">
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66926,10 +66926,10 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67724,7 +67724,7 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.8430951899654835</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68519,7 +68519,7 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.8430951899654835</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69307,14 +69307,14 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA86" t="n">
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70102,14 +70102,14 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA87" t="n">
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70897,14 +70897,14 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA88" t="n">
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71696,10 +71696,10 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72491,10 +72491,10 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73286,10 +73286,10 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74084,7 +74084,7 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.8430951899654835</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74876,10 +74876,10 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75667,14 +75667,14 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA94" t="n">
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76462,14 +76462,14 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA95" t="n">
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77257,14 +77257,14 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA96" t="n">
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78056,10 +78056,10 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78847,14 +78847,14 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA98" t="n">
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79642,14 +79642,14 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA99" t="n">
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80437,14 +80437,14 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA100" t="n">
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81236,10 +81236,10 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82034,7 +82034,7 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.8430951899654835</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82829,7 +82829,7 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.8430951899654835</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83617,14 +83617,14 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA104" t="n">
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84412,14 +84412,14 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA105" t="n">
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85207,14 +85207,14 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA106" t="n">
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86002,14 +86002,14 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA107" t="n">
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86797,14 +86797,14 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA108" t="n">
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87592,14 +87592,14 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA109" t="n">
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88387,14 +88387,14 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA110" t="n">
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89182,14 +89182,14 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA111" t="n">
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89977,14 +89977,14 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA112" t="n">
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90772,14 +90772,14 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA113" t="n">
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91567,14 +91567,14 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA114" t="n">
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92362,14 +92362,14 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA115" t="n">
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93157,14 +93157,14 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA116" t="n">
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93956,10 +93956,10 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94751,10 +94751,10 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95546,10 +95546,10 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96341,10 +96341,10 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97136,10 +97136,10 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97931,10 +97931,10 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98726,10 +98726,10 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99521,10 +99521,10 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100316,10 +100316,10 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101111,10 +101111,10 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/Attention-mamba2_repeat_3_000002.xlsx
+++ b/out/Attention-mamba2_repeat_3_000002.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.443095189965484</v>
+        <v>0.02936054971823043</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.014642784948225</v>
+        <v>0.6825578011270782</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,7 +36719,7 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37514,7 +37514,7 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38309,7 +38309,7 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39104,7 +39104,7 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39899,7 +39899,7 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.414642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40694,7 +40694,7 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.414642784948225</v>
+        <v>1.135755052535926</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41489,7 +41489,7 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.414642784948225</v>
+        <v>1.135755052535926</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42284,7 +42284,7 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.414642784948225</v>
+        <v>0.4825578011270781</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43079,7 +43079,7 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.443095189965484</v>
+        <v>0.4825578011270781</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43874,7 +43874,7 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.414642784948225</v>
+        <v>0.4825578011270781</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44669,7 +44669,7 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.414642784948225</v>
+        <v>1.135755052535926</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45464,7 +45464,7 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>2.014642784948225</v>
+        <v>1.135755052535926</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46259,7 +46259,7 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47054,7 +47054,7 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47849,7 +47849,7 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48644,7 +48644,7 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49439,7 +49439,7 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50234,7 +50234,7 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51029,7 +51029,7 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>1.414642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51824,7 +51824,7 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.414642784948225</v>
+        <v>1.135755052535926</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52619,7 +52619,7 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.414642784948225</v>
+        <v>0.4825578011270781</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53414,7 +53414,7 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.1706394502817696</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54209,7 +54209,7 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55004,7 +55004,7 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.1706394502817696</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55799,7 +55799,7 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.414642784948225</v>
+        <v>0.4825578011270781</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56594,7 +56594,7 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>1.414642784948225</v>
+        <v>1.135755052535926</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57389,7 +57389,7 @@
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58184,7 +58184,7 @@
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58979,7 +58979,7 @@
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59774,7 +59774,7 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60569,7 +60569,7 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>2.014642784948225</v>
+        <v>0.6825578011270782</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61364,7 +61364,7 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.1706394502817696</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62159,7 +62159,7 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.1706394502817696</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62954,7 +62954,7 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.1706394502817696</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63749,7 +63749,7 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.1706394502817696</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64544,7 +64544,7 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65332,14 +65332,14 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA81" t="n">
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66127,14 +66127,14 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA82" t="n">
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.1706394502817696</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66929,7 +66929,7 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.1706394502817696</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67717,14 +67717,14 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA84" t="n">
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.8430951899654835</v>
+        <v>0.02936054971823043</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68519,7 +68519,7 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.8430951899654835</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69307,14 +69307,14 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA86" t="n">
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70102,14 +70102,14 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA87" t="n">
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70897,14 +70897,14 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA88" t="n">
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.1706394502817696</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71699,7 +71699,7 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>2.014642784948225</v>
+        <v>0.6825578011270782</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72494,7 +72494,7 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73289,7 +73289,7 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>2.014642784948225</v>
+        <v>0.6825578011270782</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74084,7 +74084,7 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.8430951899654835</v>
+        <v>0.6825578011270782</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74872,14 +74872,14 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA93" t="n">
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>2.014642784948225</v>
+        <v>0.02936054971823043</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75674,7 +75674,7 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.443095189965484</v>
+        <v>0.02936054971823043</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76462,14 +76462,14 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA95" t="n">
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77257,14 +77257,14 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA96" t="n">
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.1706394502817696</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78059,7 +78059,7 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.414642784948225</v>
+        <v>-0.1706394502817696</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78847,14 +78847,14 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA98" t="n">
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.1706394502817696</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79642,14 +79642,14 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA99" t="n">
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80437,14 +80437,14 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA100" t="n">
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.1706394502817696</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81239,7 +81239,7 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>2.014642784948225</v>
+        <v>-0.1706394502817696</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82027,14 +82027,14 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA102" t="n">
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.8430951899654835</v>
+        <v>0.02936054971823043</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82829,7 +82829,7 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.8430951899654835</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83617,14 +83617,14 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA104" t="n">
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84412,14 +84412,14 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA105" t="n">
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85207,14 +85207,14 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA106" t="n">
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86002,14 +86002,14 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA107" t="n">
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86797,14 +86797,14 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA108" t="n">
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87592,14 +87592,14 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA109" t="n">
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88387,14 +88387,14 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA110" t="n">
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89182,14 +89182,14 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA111" t="n">
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89977,14 +89977,14 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA112" t="n">
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90772,14 +90772,14 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA113" t="n">
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91567,14 +91567,14 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA114" t="n">
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92362,14 +92362,14 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA115" t="n">
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.443095189965484</v>
+        <v>-0.8238367016906174</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93164,7 +93164,7 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.443095189965484</v>
+        <v>0.02936054971823043</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93959,7 +93959,7 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>2.014642784948225</v>
+        <v>0.6825578011270782</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94754,7 +94754,7 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95549,7 +95549,7 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96344,7 +96344,7 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97139,7 +97139,7 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97934,7 +97934,7 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98729,7 +98729,7 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99524,7 +99524,7 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100319,7 +100319,7 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>2.014642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101114,7 +101114,7 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.414642784948225</v>
+        <v>1.335755052535926</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/Attention-mamba2_repeat_3_000002.xlsx
+++ b/out/Attention-mamba2_repeat_3_000002.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.1725262999534607</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.2390805929899216</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.1928406059741974</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.1671648025512695</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.2027571052312851</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.1791937053203583</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.1680762320756912</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.2387964576482773</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.008074983954429626</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.2229366451501846</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.1816318184137344</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.1865399330854416</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.2257539182901382</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.2005059868097305</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.1909878104925156</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.1972320675849915</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.2077958732843399</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.2029214948415756</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.1905213445425034</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.1936653852462769</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.8238367016906174</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.203200951218605</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.8238367016906174</v>
+        <v>0.3</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.1879923194646835</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.8238367016906174</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.1656967848539352</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.8238367016906174</v>
+        <v>0.3</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.0006646998226642609</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.8238367016906174</v>
+        <v>0.3</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.2591363787651062</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.8238367016906174</v>
+        <v>0.16</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.2359365969896317</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.2458945959806442</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.2273985296487808</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.1982779949903488</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.1896355301141739</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.1989463120698929</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.1840276420116425</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.8238367016906174</v>
+        <v>0.16</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.1857373416423798</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.8238367016906174</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.1914078146219254</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.8238367016906174</v>
+        <v>0.3</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.2205565422773361</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.8238367016906174</v>
+        <v>0.16</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.0008901767432689667</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.8238367016906174</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.2703928649425507</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.8238367016906174</v>
+        <v>0.16</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.2276727110147476</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.02936054971823043</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.008374247699975967</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.6825578011270782</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.02813491597771645</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.335755052535926</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.03038420528173447</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.335755052535926</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.02489458024501801</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.335755052535926</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.01146969571709633</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.335755052535926</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,10 +36716,10 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.0284949317574501</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.335755052535926</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37511,10 +37511,10 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.02415842935442924</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.335755052535926</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38306,10 +38306,10 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.01756633818149567</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.335755052535926</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39101,10 +39101,10 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.005438771098852158</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.335755052535926</v>
+        <v>-0.16</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39896,10 +39896,10 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.02025562897324562</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.335755052535926</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40691,10 +40691,10 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.004007685929536819</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.135755052535926</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41486,10 +41486,10 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.03013266995549202</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.135755052535926</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42281,10 +42281,10 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.005712132900953293</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.4825578011270781</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43076,10 +43076,10 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.003918427973985672</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.4825578011270781</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43871,10 +43871,10 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.03845097497105598</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.4825578011270781</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44666,10 +44666,10 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.107150062918663</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.135755052535926</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45461,10 +45461,10 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.06337390840053558</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.135755052535926</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46256,10 +46256,10 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.1644448637962341</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.335755052535926</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47051,10 +47051,10 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.1315154582262039</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.335755052535926</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47846,10 +47846,10 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.03874900192022324</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.335755052535926</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48641,10 +48641,10 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.0384829193353653</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.335755052535926</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49436,10 +49436,10 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.04219401627779007</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.335755052535926</v>
+        <v>-0.16</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50231,10 +50231,10 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.01349325105547905</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.335755052535926</v>
+        <v>-0.16</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51026,10 +51026,10 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.04608337581157684</v>
       </c>
       <c r="JB63" t="n">
-        <v>1.335755052535926</v>
+        <v>-0.16</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51821,10 +51821,10 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.1150024682283401</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.135755052535926</v>
+        <v>-0.3</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52616,10 +52616,10 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.01934134215116501</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.4825578011270781</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53411,10 +53411,10 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.006229951977729797</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.1706394502817696</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54206,10 +54206,10 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.0132221095263958</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55001,10 +55001,10 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.009462077170610428</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.1706394502817696</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55796,10 +55796,10 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.02408770099282265</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.4825578011270781</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56591,10 +56591,10 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.07198405265808105</v>
       </c>
       <c r="JB70" t="n">
-        <v>1.135755052535926</v>
+        <v>-0.16</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57386,10 +57386,10 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.1060570329427719</v>
       </c>
       <c r="JB71" t="n">
-        <v>1.335755052535926</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58181,10 +58181,10 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.1060114055871964</v>
       </c>
       <c r="JB72" t="n">
-        <v>1.335755052535926</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58976,10 +58976,10 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.1816188246011734</v>
       </c>
       <c r="JB73" t="n">
-        <v>1.335755052535926</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59771,10 +59771,10 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.156184047460556</v>
       </c>
       <c r="JB74" t="n">
-        <v>1.335755052535926</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60566,10 +60566,10 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.1799453347921371</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.6825578011270782</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61361,10 +61361,10 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.2013813406229019</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.1706394502817696</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62156,10 +62156,10 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.2071151882410049</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.1706394502817696</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62951,10 +62951,10 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.187160462141037</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.1706394502817696</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63746,10 +63746,10 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>0.1815002411603928</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.1706394502817696</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64541,10 +64541,10 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.202581599354744</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65336,10 +65336,10 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.1308097094297409</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.3</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66131,10 +66131,10 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>0.1795871704816818</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.1706394502817696</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66926,10 +66926,10 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.1843878775835037</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.1706394502817696</v>
+        <v>-0.16</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67717,14 +67717,14 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>0.1693585216999054</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.02936054971823043</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68516,10 +68516,10 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>0.1806481927633286</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.8238367016906174</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69311,10 +69311,10 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>0.1782266497612</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.8238367016906174</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70106,10 +70106,10 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.2041536718606949</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.8238367016906174</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70901,10 +70901,10 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>0.1866398006677628</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.1706394502817696</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71696,10 +71696,10 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.1678351610898972</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.6825578011270782</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72491,10 +72491,10 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.09026665985584259</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.335755052535926</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73286,10 +73286,10 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.197470411658287</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.6825578011270782</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74081,10 +74081,10 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>0.1857731193304062</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.6825578011270782</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74872,14 +74872,14 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.1627668738365173</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.02936054971823043</v>
+        <v>-0.3</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75667,14 +75667,14 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.2568624019622803</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.02936054971823043</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76466,10 +76466,10 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.2198769897222519</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77261,10 +77261,10 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.2031301409006119</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.1706394502817696</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78056,10 +78056,10 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.1797216087579727</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.1706394502817696</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78851,10 +78851,10 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.2477511018514633</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.1706394502817696</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79646,10 +79646,10 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.2482752948999405</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80441,10 +80441,10 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.2218307703733444</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.1706394502817696</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81236,10 +81236,10 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.1843813061714172</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.1706394502817696</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82027,14 +82027,14 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.2081441432237625</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.02936054971823043</v>
+        <v>0.16</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82826,10 +82826,10 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.2308700829744339</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.8238367016906174</v>
+        <v>0.16</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83621,10 +83621,10 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>0.1851251572370529</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84416,10 +84416,10 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.2310165017843246</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85211,10 +85211,10 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.240830734372139</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86006,10 +86006,10 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.2399934381246567</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86801,10 +86801,10 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.2181676179170609</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87596,10 +87596,10 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.2091472893953323</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88391,10 +88391,10 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.2201374918222427</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89186,10 +89186,10 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.2059936076402664</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89981,10 +89981,10 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>0.1851545870304108</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90776,10 +90776,10 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.2222508639097214</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91571,10 +91571,10 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.2359763830900192</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92366,10 +92366,10 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.2194271832704544</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.8238367016906174</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93157,14 +93157,14 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.2173265069723129</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.02936054971823043</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93956,10 +93956,10 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.1183101683855057</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.6825578011270782</v>
+        <v>0.3</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94751,10 +94751,10 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.1044569462537766</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.335755052535926</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95546,10 +95546,10 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.04465494304895401</v>
       </c>
       <c r="JB119" t="n">
-        <v>1.335755052535926</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96341,10 +96341,10 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.06750133633613586</v>
       </c>
       <c r="JB120" t="n">
-        <v>1.335755052535926</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97136,10 +97136,10 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.06318137794733047</v>
       </c>
       <c r="JB121" t="n">
-        <v>1.335755052535926</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97931,10 +97931,10 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.1388841867446899</v>
       </c>
       <c r="JB122" t="n">
-        <v>1.335755052535926</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98726,10 +98726,10 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.1637655645608902</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.335755052535926</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99521,10 +99521,10 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.1396480947732925</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.335755052535926</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100316,10 +100316,10 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.1795372813940048</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.335755052535926</v>
+        <v>0.7199999999999995</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101111,10 +101111,10 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.05382882803678513</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.335755052535926</v>
+        <v>-0.02000000000000046</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/Attention-mamba2_repeat_3_000002.xlsx
+++ b/out/Attention-mamba2_repeat_3_000002.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>-0.1725262999534607</v>
+        <v>-0.1724452376365662</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.9999999999999998</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>-0.2390805929899216</v>
+        <v>-0.2393495291471481</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.9999999999999998</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>-0.1928406059741974</v>
+        <v>-0.1928623020648956</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.9999999999999998</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>-0.1671648025512695</v>
+        <v>-0.1669428944587708</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.9999999999999998</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>-0.2027571052312851</v>
+        <v>-0.202635869383812</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.9999999999999998</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>-0.1791937053203583</v>
+        <v>-0.1789060235023499</v>
       </c>
       <c r="JB7" t="n">
         <v>-0.9999999999999998</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>-0.1680762320756912</v>
+        <v>-0.167760506272316</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.7199999999999999</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>-0.2387964576482773</v>
+        <v>-0.2389766722917557</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.7199999999999999</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>-0.008074983954429626</v>
+        <v>-0.009575076401233673</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.7199999999999999</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>-0.2229366451501846</v>
+        <v>-0.2229984849691391</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.1199999999999999</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>-0.1816318184137344</v>
+        <v>-0.1810080111026764</v>
       </c>
       <c r="JB12" t="n">
         <v>-0.1199999999999999</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>-0.1865399330854416</v>
+        <v>-0.1857346147298813</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.3999999999999999</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>-0.2257539182901382</v>
+        <v>-0.2249947935342789</v>
       </c>
       <c r="JB14" t="n">
         <v>-0.8599999999999999</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>-0.2005059868097305</v>
+        <v>-0.1997466236352921</v>
       </c>
       <c r="JB15" t="n">
         <v>-0.8599999999999999</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>-0.1909878104925156</v>
+        <v>-0.190269872546196</v>
       </c>
       <c r="JB16" t="n">
         <v>-0.8599999999999999</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>-0.1972320675849915</v>
+        <v>-0.1964767575263977</v>
       </c>
       <c r="JB17" t="n">
         <v>-0.8599999999999999</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>-0.2077958732843399</v>
+        <v>-0.2070235460996628</v>
       </c>
       <c r="JB18" t="n">
         <v>-0.7199999999999999</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>-0.2029214948415756</v>
+        <v>-0.2021853476762772</v>
       </c>
       <c r="JB19" t="n">
         <v>-0.1199999999999999</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>-0.1905213445425034</v>
+        <v>-0.1898053139448166</v>
       </c>
       <c r="JB20" t="n">
         <v>-0.1199999999999999</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>-0.1936653852462769</v>
+        <v>-0.1929276138544083</v>
       </c>
       <c r="JB21" t="n">
         <v>0.02000000000000007</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>-0.203200951218605</v>
+        <v>-0.2024975568056107</v>
       </c>
       <c r="JB22" t="n">
         <v>0.3</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>-0.1879923194646835</v>
+        <v>-0.1873227208852768</v>
       </c>
       <c r="JB23" t="n">
         <v>0.4399999999999999</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>-0.1656967848539352</v>
+        <v>-0.1652115136384964</v>
       </c>
       <c r="JB24" t="n">
         <v>0.3</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>-0.0006646998226642609</v>
+        <v>-0.002055257558822632</v>
       </c>
       <c r="JB25" t="n">
         <v>0.3</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>-0.2591363787651062</v>
+        <v>-0.2589718699455261</v>
       </c>
       <c r="JB26" t="n">
         <v>0.16</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>-0.2359365969896317</v>
+        <v>-0.2353924363851547</v>
       </c>
       <c r="JB27" t="n">
         <v>-0.1199999999999999</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>-0.2458945959806442</v>
+        <v>-0.2452041655778885</v>
       </c>
       <c r="JB28" t="n">
         <v>-0.9999999999999998</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>-0.2273985296487808</v>
+        <v>-0.2265597730875015</v>
       </c>
       <c r="JB29" t="n">
         <v>-0.8599999999999999</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>-0.1982779949903488</v>
+        <v>-0.1975148916244507</v>
       </c>
       <c r="JB30" t="n">
         <v>-0.8599999999999999</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>-0.1896355301141739</v>
+        <v>-0.1889102309942245</v>
       </c>
       <c r="JB31" t="n">
         <v>-0.7199999999999999</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>-0.1989463120698929</v>
+        <v>-0.1982885748147964</v>
       </c>
       <c r="JB32" t="n">
         <v>-0.5799999999999998</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>-0.1840276420116425</v>
+        <v>-0.1833620369434357</v>
       </c>
       <c r="JB33" t="n">
         <v>0.16</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>-0.1857373416423798</v>
+        <v>-0.1850629299879074</v>
       </c>
       <c r="JB34" t="n">
         <v>0.02000000000000007</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>-0.1914078146219254</v>
+        <v>-0.1906020939350128</v>
       </c>
       <c r="JB35" t="n">
         <v>0.3</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>-0.2205565422773361</v>
+        <v>-0.2202016562223434</v>
       </c>
       <c r="JB36" t="n">
         <v>0.16</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>-0.0008901767432689667</v>
+        <v>-0.00207885354757309</v>
       </c>
       <c r="JB37" t="n">
         <v>0.02000000000000007</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>-0.2703928649425507</v>
+        <v>-0.2702690660953522</v>
       </c>
       <c r="JB38" t="n">
         <v>0.16</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>-0.2276727110147476</v>
+        <v>-0.227534607052803</v>
       </c>
       <c r="JB39" t="n">
         <v>0.4399999999999999</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0.008374247699975967</v>
+        <v>0.006983488798141479</v>
       </c>
       <c r="JB40" t="n">
         <v>0.4399999999999999</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0.02813491597771645</v>
+        <v>0.02643470279872417</v>
       </c>
       <c r="JB41" t="n">
         <v>0.7199999999999999</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0.03038420528173447</v>
+        <v>0.02948193252086639</v>
       </c>
       <c r="JB42" t="n">
         <v>0.9999999999999998</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.02489458024501801</v>
+        <v>0.02393747866153717</v>
       </c>
       <c r="JB43" t="n">
         <v>0.9999999999999998</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0.01146969571709633</v>
+        <v>0.01049789413809776</v>
       </c>
       <c r="JB44" t="n">
         <v>0.8599999999999999</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.0284949317574501</v>
+        <v>0.02711230888962746</v>
       </c>
       <c r="JB45" t="n">
         <v>0.7199999999999999</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0.02415842935442924</v>
+        <v>0.02318987995386124</v>
       </c>
       <c r="JB46" t="n">
         <v>0.5799999999999998</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0.01756633818149567</v>
+        <v>0.01614625006914139</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.02000000000000007</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0.005438771098852158</v>
+        <v>0.005564205348491669</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.16</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0.02025562897324562</v>
+        <v>0.01972028985619545</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.02000000000000007</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0.004007685929536819</v>
+        <v>0.004148062318563461</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.02000000000000007</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0.03013266995549202</v>
+        <v>0.0291619747877121</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.02000000000000007</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0.005712132900953293</v>
+        <v>0.004617493599653244</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.02000000000000007</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>-0.003918427973985672</v>
+        <v>-0.004086192697286606</v>
       </c>
       <c r="JB53" t="n">
         <v>0.7199999999999999</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0.03845097497105598</v>
+        <v>0.03857867047190666</v>
       </c>
       <c r="JB54" t="n">
         <v>0.7199999999999999</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0.107150062918663</v>
+        <v>0.1077644228935242</v>
       </c>
       <c r="JB55" t="n">
         <v>0.8599999999999999</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0.06337390840053558</v>
+        <v>0.06378044933080673</v>
       </c>
       <c r="JB56" t="n">
         <v>0.9999999999999998</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0.1644448637962341</v>
+        <v>0.1651104837656021</v>
       </c>
       <c r="JB57" t="n">
         <v>0.9999999999999998</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0.1315154582262039</v>
+        <v>0.1322715431451797</v>
       </c>
       <c r="JB58" t="n">
         <v>0.8599999999999999</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0.03874900192022324</v>
+        <v>0.03919458389282227</v>
       </c>
       <c r="JB59" t="n">
         <v>0.7199999999999999</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0.0384829193353653</v>
+        <v>0.03873716294765472</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.02000000000000007</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0.04219401627779007</v>
+        <v>0.04265342652797699</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.16</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0.01349325105547905</v>
+        <v>0.01367956772446632</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.16</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0.04608337581157684</v>
+        <v>0.04625371843576431</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.16</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0.1150024682283401</v>
+        <v>0.1156265288591385</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.3</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0.01934134215116501</v>
+        <v>0.01974757388234138</v>
       </c>
       <c r="JB65" t="n">
         <v>-0.4399999999999999</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>-0.006229951977729797</v>
+        <v>-0.006221495568752289</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.5799999999999998</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>-0.0132221095263958</v>
+        <v>-0.01339599117636681</v>
       </c>
       <c r="JB67" t="n">
         <v>-0.8599999999999999</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>-0.009462077170610428</v>
+        <v>-0.00965055450797081</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.7199999999999999</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0.02408770099282265</v>
+        <v>0.02415188774466515</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.4399999999999999</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0.07198405265808105</v>
+        <v>0.07269641757011414</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.16</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0.1060570329427719</v>
+        <v>0.1066823303699493</v>
       </c>
       <c r="JB71" t="n">
         <v>0.7199999999999999</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0.1060114055871964</v>
+        <v>0.1063968986272812</v>
       </c>
       <c r="JB72" t="n">
         <v>0.9999999999999998</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0.1816188246011734</v>
+        <v>0.1822461038827896</v>
       </c>
       <c r="JB73" t="n">
         <v>0.9999999999999998</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0.156184047460556</v>
+        <v>0.1567977517843246</v>
       </c>
       <c r="JB74" t="n">
         <v>0.7199999999999999</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0.1799453347921371</v>
+        <v>0.1805190145969391</v>
       </c>
       <c r="JB75" t="n">
         <v>0.4399999999999999</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>-0.2013813406229019</v>
+        <v>-0.2006088048219681</v>
       </c>
       <c r="JB76" t="n">
         <v>0.4399999999999999</v>
@@ -62156,10 +62156,10 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>-0.2071151882410049</v>
+        <v>-0.2063618153333664</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.1600000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62951,10 +62951,10 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0.187160462141037</v>
+        <v>0.1877137720584869</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.4399999999999999</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63746,10 +63746,10 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0.1815002411603928</v>
+        <v>-0.1651441305875778</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.4399999999999999</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64541,10 +64541,10 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>-0.202581599354744</v>
+        <v>-0.2019201964139938</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.1600000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65336,10 +65336,10 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>-0.1308097094297409</v>
+        <v>-0.2102878540754318</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.3</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66131,10 +66131,10 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0.1795871704816818</v>
+        <v>-0.2125053256750107</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.4399999999999999</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66926,10 +66926,10 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0.1843878775835037</v>
+        <v>0.1849410235881805</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.16</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67721,10 +67721,10 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0.1693585216999054</v>
+        <v>-0.2128601521253586</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.7199999999999999</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68516,10 +68516,10 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0.1806481927633286</v>
+        <v>-0.04636790230870247</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.4399999999999999</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69311,10 +69311,10 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0.1782266497612</v>
+        <v>-0.218010202050209</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.5799999999999998</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70106,10 +70106,10 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>-0.2041536718606949</v>
+        <v>-0.2036167830228806</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.5799999999999998</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70901,10 +70901,10 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0.1866398006677628</v>
+        <v>-0.2697587013244629</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.16</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0.1678351610898972</v>
+        <v>0.1685210019350052</v>
       </c>
       <c r="JB89" t="n">
         <v>0.4399999999999999</v>
@@ -72491,10 +72491,10 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0.09026665985584259</v>
+        <v>0.09073060750961304</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.7199999999999999</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73286,10 +73286,10 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.197470411658287</v>
+        <v>0.1980422288179398</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.5799999999999998</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0.1857731193304062</v>
+        <v>-0.2671408951282501</v>
       </c>
       <c r="JB92" t="n">
         <v>0.4399999999999999</v>
@@ -74876,10 +74876,10 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0.1627668738365173</v>
+        <v>0.1633280664682388</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.3</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75671,10 +75671,10 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>-0.2568624019622803</v>
+        <v>-0.2564050257205963</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.5799999999999998</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76466,10 +76466,10 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>-0.2198769897222519</v>
+        <v>-0.2195103317499161</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77261,10 +77261,10 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>-0.2031301409006119</v>
+        <v>-0.2024452835321426</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78056,10 +78056,10 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0.1797216087579727</v>
+        <v>0.1802641600370407</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78851,10 +78851,10 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>-0.2477511018514633</v>
+        <v>-0.2471389919519424</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79646,10 +79646,10 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>-0.2482752948999405</v>
+        <v>-0.2479464262723923</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.5799999999999998</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>-0.2218307703733444</v>
+        <v>-0.2212096601724625</v>
       </c>
       <c r="JB100" t="n">
         <v>-0.7199999999999999</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.1843813061714172</v>
+        <v>0.1848869770765305</v>
       </c>
       <c r="JB101" t="n">
         <v>-0.7199999999999999</v>
@@ -82031,10 +82031,10 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>-0.2081441432237625</v>
+        <v>-0.2076664417982101</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.16</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82826,10 +82826,10 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>-0.2308700829744339</v>
+        <v>-0.2303903549909592</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.16</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83621,10 +83621,10 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0.1851251572370529</v>
+        <v>-0.2334770411252975</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84416,10 +84416,10 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>-0.2310165017843246</v>
+        <v>-0.2304946631193161</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85211,10 +85211,10 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>-0.240830734372139</v>
+        <v>-0.2456637173891068</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>-0.2399934381246567</v>
+        <v>-0.2396095544099808</v>
       </c>
       <c r="JB107" t="n">
         <v>-0.9999999999999998</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>-0.2181676179170609</v>
+        <v>-0.2177971452474594</v>
       </c>
       <c r="JB108" t="n">
         <v>-0.9999999999999998</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>-0.2091472893953323</v>
+        <v>-0.2087608724832535</v>
       </c>
       <c r="JB109" t="n">
         <v>-0.9999999999999998</v>
@@ -88391,10 +88391,10 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>-0.2201374918222427</v>
+        <v>-0.2198158949613571</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89186,10 +89186,10 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>-0.2059936076402664</v>
+        <v>-0.205506756901741</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89981,10 +89981,10 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.1851545870304108</v>
+        <v>-0.2485454231500626</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90776,10 +90776,10 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>-0.2222508639097214</v>
+        <v>-0.2217694967985153</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91571,10 +91571,10 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>-0.2359763830900192</v>
+        <v>-0.2356127053499222</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92366,10 +92366,10 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>-0.2194271832704544</v>
+        <v>-0.2189719825983047</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.2599999999999998</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93161,10 +93161,10 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>-0.2173265069723129</v>
+        <v>-0.2166583091020584</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.02000000000000007</v>
+        <v>0.16</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93956,10 +93956,10 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.1183101683855057</v>
+        <v>0.1188861280679703</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.3</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94751,10 +94751,10 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.1044569462537766</v>
+        <v>0.105065330862999</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.5799999999999998</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95546,10 +95546,10 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.04465494304895401</v>
+        <v>0.04507056996226311</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.8599999999999999</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0.06750133633613586</v>
+        <v>0.06877560168504715</v>
       </c>
       <c r="JB120" t="n">
         <v>0.9999999999999998</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0.06318137794733047</v>
+        <v>0.06357589364051819</v>
       </c>
       <c r="JB121" t="n">
         <v>0.9999999999999998</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.1388841867446899</v>
+        <v>0.1394149959087372</v>
       </c>
       <c r="JB122" t="n">
         <v>0.9999999999999998</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.1637655645608902</v>
+        <v>0.1643367111682892</v>
       </c>
       <c r="JB123" t="n">
         <v>0.9999999999999998</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.1396480947732925</v>
+        <v>0.1401719152927399</v>
       </c>
       <c r="JB124" t="n">
         <v>0.8599999999999999</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0.1795372813940048</v>
+        <v>0.1801003962755203</v>
       </c>
       <c r="JB125" t="n">
         <v>0.7199999999999995</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.05382882803678513</v>
+        <v>0.05404514074325562</v>
       </c>
       <c r="JB126" t="n">
         <v>-0.02000000000000046</v>
